--- a/Kata Kunci.xlsx
+++ b/Kata Kunci.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LNPRT\Scrapping\Berita\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Argo\!!2026\AI\Antigravity\berita\Web-Scraping-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A33B53-FE5E-48EA-B1FE-EF4DDE46FE1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A204505-CF1C-4514-9374-40474075A862}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" xr2:uid="{A8968677-769D-4485-84B0-F2D4272DC42E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" xr2:uid="{A8968677-769D-4485-84B0-F2D4272DC42E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>Organisasi Kemasyarakatan</t>
   </si>
@@ -51,18 +51,6 @@
     <t>Nahdlatul Ulama</t>
   </si>
   <si>
-    <t>Palang Merah Indonesia</t>
-  </si>
-  <si>
-    <t>PMI</t>
-  </si>
-  <si>
-    <t>Kitabisa</t>
-  </si>
-  <si>
-    <t>RumahZakat</t>
-  </si>
-  <si>
     <t>Panti Asuhan</t>
   </si>
   <si>
@@ -81,36 +69,9 @@
     <t>Persatuan Buruh</t>
   </si>
   <si>
-    <t>Sanggar</t>
-  </si>
-  <si>
     <t>Parpol</t>
   </si>
   <si>
-    <t>Masjid</t>
-  </si>
-  <si>
-    <t>Musala</t>
-  </si>
-  <si>
-    <t>Gereja</t>
-  </si>
-  <si>
-    <t>Pura</t>
-  </si>
-  <si>
-    <t>Vihara</t>
-  </si>
-  <si>
-    <t>Kelenteng</t>
-  </si>
-  <si>
-    <t>Klenteng</t>
-  </si>
-  <si>
-    <t>Majelis Taklim</t>
-  </si>
-  <si>
     <t>Pemilu</t>
   </si>
   <si>
@@ -120,39 +81,12 @@
     <t>Pilpres</t>
   </si>
   <si>
-    <t>PSSI</t>
-  </si>
-  <si>
-    <t>PBSI</t>
-  </si>
-  <si>
-    <t>PBVSI</t>
-  </si>
-  <si>
-    <t>Buka Bersama</t>
-  </si>
-  <si>
     <t>Nyepi</t>
   </si>
   <si>
     <t>Imlek</t>
   </si>
   <si>
-    <t>Shalat</t>
-  </si>
-  <si>
-    <t>Sholat</t>
-  </si>
-  <si>
-    <t>Mushola</t>
-  </si>
-  <si>
-    <t>Mesjid</t>
-  </si>
-  <si>
-    <t>Ied</t>
-  </si>
-  <si>
     <t>Paskah</t>
   </si>
   <si>
@@ -171,9 +105,6 @@
     <t>Muktamar</t>
   </si>
   <si>
-    <t>Bantuan</t>
-  </si>
-  <si>
     <t>Bencana</t>
   </si>
   <si>
@@ -192,24 +123,12 @@
     <t>Maulid</t>
   </si>
   <si>
-    <t>ZIS</t>
-  </si>
-  <si>
-    <t>Infak</t>
-  </si>
-  <si>
-    <t>Sedekah</t>
-  </si>
-  <si>
     <t>Kampanye</t>
   </si>
   <si>
     <t>Kurban</t>
   </si>
   <si>
-    <t>Qurban</t>
-  </si>
-  <si>
     <t>Rakerda</t>
   </si>
   <si>
@@ -255,13 +174,34 @@
     <t>Ikatan Pekerja</t>
   </si>
   <si>
-    <t>IBI</t>
-  </si>
-  <si>
-    <t>IDI</t>
-  </si>
-  <si>
-    <t>Ikatan Mahasiswa</t>
+    <t>Konbes</t>
+  </si>
+  <si>
+    <t>Panti Sosial</t>
+  </si>
+  <si>
+    <t>Bantuan Panti</t>
+  </si>
+  <si>
+    <t>MayDay</t>
+  </si>
+  <si>
+    <t>Festival</t>
+  </si>
+  <si>
+    <t>Pameran</t>
+  </si>
+  <si>
+    <t>Komunitas</t>
+  </si>
+  <si>
+    <t>LNPRT</t>
+  </si>
+  <si>
+    <t>Gempa</t>
+  </si>
+  <si>
+    <t>Tsunami</t>
   </si>
 </sst>
 </file>
@@ -613,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF6A9227-58DB-47F7-8EA9-671193496A79}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -645,7 +585,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -653,22 +593,22 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -676,239 +616,155 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
         <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="G8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>77</v>
+      <c r="A10" t="s">
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>78</v>
+      <c r="A11" t="s">
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="G22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="G23" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Kata Kunci.xlsx
+++ b/Kata Kunci.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Argo\!!2026\AI\Antigravity\berita\Web-Scraping-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A204505-CF1C-4514-9374-40474075A862}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C2440A-4011-4023-A5A2-2CB702E21643}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" xr2:uid="{A8968677-769D-4485-84B0-F2D4272DC42E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" activeTab="1" xr2:uid="{A8968677-769D-4485-84B0-F2D4272DC42E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="keyword" sheetId="1" r:id="rId1"/>
+    <sheet name="persepsi" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
   <si>
     <t>Organisasi Kemasyarakatan</t>
   </si>
@@ -202,6 +203,90 @@
   </si>
   <si>
     <t>Tsunami</t>
+  </si>
+  <si>
+    <t>naik</t>
+  </si>
+  <si>
+    <t>turun</t>
+  </si>
+  <si>
+    <t>bertambah</t>
+  </si>
+  <si>
+    <t>berkurang</t>
+  </si>
+  <si>
+    <t>meningkat</t>
+  </si>
+  <si>
+    <t>menurun</t>
+  </si>
+  <si>
+    <t>tumbuh</t>
+  </si>
+  <si>
+    <t>melambat</t>
+  </si>
+  <si>
+    <t>lebih besar</t>
+  </si>
+  <si>
+    <t>lebih kecil</t>
+  </si>
+  <si>
+    <t>lebih banyak</t>
+  </si>
+  <si>
+    <t>lebih sedikit</t>
+  </si>
+  <si>
+    <t>percepatan</t>
+  </si>
+  <si>
+    <t>perlambatan</t>
+  </si>
+  <si>
+    <t>melesat</t>
+  </si>
+  <si>
+    <t>anjlok</t>
+  </si>
+  <si>
+    <t>lebih cepat</t>
+  </si>
+  <si>
+    <t>lebih lambat</t>
+  </si>
+  <si>
+    <t>lebih tinggi</t>
+  </si>
+  <si>
+    <t>lebih rendah</t>
+  </si>
+  <si>
+    <t>lebih luas</t>
+  </si>
+  <si>
+    <t>lebih sempit</t>
+  </si>
+  <si>
+    <t>meluas</t>
+  </si>
+  <si>
+    <t>menyempit</t>
+  </si>
+  <si>
+    <t>lebih kuat</t>
+  </si>
+  <si>
+    <t>lebih lemah</t>
+  </si>
+  <si>
+    <t>menguat</t>
+  </si>
+  <si>
+    <t>melemah</t>
   </si>
 </sst>
 </file>
@@ -770,4 +855,137 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733CDB76-AE75-4AF6-86E2-6980EF40DE66}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>